--- a/BOM/Закупочный лист.xlsx
+++ b/BOM/Закупочный лист.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\PDU_Control_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5E08FE-5CE9-41C6-B056-676DFBD70E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77533A6A-1AD5-4740-A46B-CE1C4EC22453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="157">
   <si>
     <t>Reference</t>
   </si>
@@ -479,6 +479,18 @@
   </si>
   <si>
     <t>Электронщик</t>
+  </si>
+  <si>
+    <t>ЧИП ДИП</t>
+  </si>
+  <si>
+    <t>Счет сформирован</t>
+  </si>
+  <si>
+    <t>Счет оплачен</t>
+  </si>
+  <si>
+    <t>Получено</t>
   </si>
 </sst>
 </file>
@@ -499,7 +511,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -509,6 +521,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,10 +569,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -556,6 +576,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -860,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" customWidth="1"/>
@@ -873,7 +895,7 @@
     <col min="11" max="11" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -898,13 +920,13 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>151</v>
       </c>
     </row>
@@ -925,11 +947,11 @@
         <v>17</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="5">
+      <c r="I2" s="4"/>
+      <c r="J2" s="3">
         <v>100</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -950,11 +972,11 @@
         <v>9</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="5">
+      <c r="I3" s="4"/>
+      <c r="J3" s="3">
         <v>50</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -975,11 +997,11 @@
         <v>14</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="5">
+      <c r="I4" s="4"/>
+      <c r="J4" s="3">
         <v>100</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1000,11 +1022,11 @@
         <v>2</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="5">
+      <c r="I5" s="4"/>
+      <c r="J5" s="3">
         <v>50</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1025,11 +1047,11 @@
         <v>8</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="5">
+      <c r="I6" s="4"/>
+      <c r="J6" s="3">
         <v>50</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1050,11 +1072,11 @@
         <v>4</v>
       </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="5">
+      <c r="I7" s="4"/>
+      <c r="J7" s="3">
         <v>50</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1075,11 +1097,11 @@
         <v>2</v>
       </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="5">
+      <c r="I8" s="4"/>
+      <c r="J8" s="3">
         <v>10</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1100,11 +1122,11 @@
         <v>2</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="5">
+      <c r="I9" s="4"/>
+      <c r="J9" s="3">
         <v>10</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1127,11 +1149,11 @@
         <v>2</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="5">
+      <c r="I10" s="4"/>
+      <c r="J10" s="3">
         <v>10</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1154,11 +1176,11 @@
         <v>2</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="5">
+      <c r="I11" s="4"/>
+      <c r="J11" s="3">
         <v>5</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1179,11 +1201,11 @@
         <v>6</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="5">
+      <c r="I12" s="4"/>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1206,9 +1228,13 @@
         <v>1</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="3">
+        <v>5</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1229,9 +1255,13 @@
         <v>1</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="3">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1252,9 +1282,13 @@
         <v>1</v>
       </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="3">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1275,9 +1309,13 @@
         <v>1</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="3">
+        <v>5</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1296,11 +1334,11 @@
         <v>1</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="5">
+      <c r="I17" s="4"/>
+      <c r="J17" s="3">
         <v>10</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1321,11 +1359,11 @@
         <v>1</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="5">
+      <c r="I18" s="4"/>
+      <c r="J18" s="3">
         <v>10</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1346,11 +1384,11 @@
         <v>1</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="5">
+      <c r="I19" s="4"/>
+      <c r="J19" s="3">
         <v>10</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1375,11 +1413,11 @@
         <v>1</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="5">
+      <c r="I20" s="4"/>
+      <c r="J20" s="3">
         <v>5</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1404,9 +1442,13 @@
         <v>1</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="3">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1429,11 +1471,11 @@
         <v>1</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="5">
+      <c r="I22" s="4"/>
+      <c r="J22" s="3">
         <v>10</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1458,11 +1500,11 @@
         <v>5</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="5">
+      <c r="I23" s="4"/>
+      <c r="J23" s="3">
         <v>20</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1487,11 +1529,11 @@
         <v>5</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="5">
+      <c r="I24" s="4"/>
+      <c r="J24" s="3">
         <v>20</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1516,11 +1558,11 @@
         <v>7</v>
       </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="5">
+      <c r="I25" s="4"/>
+      <c r="J25" s="3">
         <v>20</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="K25" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1545,11 +1587,11 @@
         <v>12</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="5">
+      <c r="I26" s="4"/>
+      <c r="J26" s="3">
         <v>30</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1574,11 +1616,11 @@
         <v>1</v>
       </c>
       <c r="H27" s="1"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="5">
+      <c r="I27" s="4"/>
+      <c r="J27" s="3">
         <v>3</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="K27" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1603,11 +1645,11 @@
         <v>3</v>
       </c>
       <c r="H28" s="1"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="5">
+      <c r="I28" s="4"/>
+      <c r="J28" s="3">
         <v>10</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1632,11 +1674,11 @@
         <v>1</v>
       </c>
       <c r="H29" s="1"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="5">
+      <c r="I29" s="4"/>
+      <c r="J29" s="3">
         <v>3</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1661,11 +1703,11 @@
         <v>1</v>
       </c>
       <c r="H30" s="1"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="5">
+      <c r="I30" s="4"/>
+      <c r="J30" s="3">
         <v>3</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="K30" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1690,11 +1732,11 @@
         <v>2</v>
       </c>
       <c r="H31" s="1"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="5">
+      <c r="I31" s="4"/>
+      <c r="J31" s="3">
         <v>10</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1719,11 +1761,11 @@
         <v>13</v>
       </c>
       <c r="H32" s="1"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="5">
+      <c r="I32" s="4"/>
+      <c r="J32" s="3">
         <v>30</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="K32" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1750,9 +1792,13 @@
         <v>1</v>
       </c>
       <c r="H33" s="1"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="3">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -1773,9 +1819,13 @@
         <v>1</v>
       </c>
       <c r="H34" s="1"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="3">
+        <v>5</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="35" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -1798,9 +1848,13 @@
         <v>5</v>
       </c>
       <c r="H35" s="1"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="3">
+        <v>15</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -1823,11 +1877,11 @@
         <v>5</v>
       </c>
       <c r="H36" s="1"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="5">
+      <c r="I36" s="4"/>
+      <c r="J36" s="3">
         <v>20</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="K36" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1848,11 +1902,11 @@
         <v>18</v>
       </c>
       <c r="H37" s="1"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="5">
+      <c r="I37" s="4"/>
+      <c r="J37" s="3">
         <v>100</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1873,11 +1927,11 @@
         <v>11</v>
       </c>
       <c r="H38" s="1"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="5">
+      <c r="I38" s="4"/>
+      <c r="J38" s="3">
         <v>100</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1898,11 +1952,11 @@
         <v>6</v>
       </c>
       <c r="H39" s="1"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="5">
+      <c r="I39" s="4"/>
+      <c r="J39" s="3">
         <v>100</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="K39" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1923,11 +1977,11 @@
         <v>1</v>
       </c>
       <c r="H40" s="1"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="5">
+      <c r="I40" s="4"/>
+      <c r="J40" s="3">
         <v>100</v>
       </c>
-      <c r="K40" s="4" t="s">
+      <c r="K40" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1948,11 +2002,11 @@
         <v>6</v>
       </c>
       <c r="H41" s="1"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="5">
+      <c r="I41" s="4"/>
+      <c r="J41" s="3">
         <v>50</v>
       </c>
-      <c r="K41" s="4" t="s">
+      <c r="K41" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1973,11 +2027,11 @@
         <v>3</v>
       </c>
       <c r="H42" s="1"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="5">
+      <c r="I42" s="4"/>
+      <c r="J42" s="3">
         <v>50</v>
       </c>
-      <c r="K42" s="4" t="s">
+      <c r="K42" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1998,11 +2052,11 @@
         <v>4</v>
       </c>
       <c r="H43" s="1"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="5">
+      <c r="I43" s="4"/>
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="K43" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2023,11 +2077,11 @@
         <v>1</v>
       </c>
       <c r="H44" s="1"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="5">
+      <c r="I44" s="4"/>
+      <c r="J44" s="3">
         <v>10</v>
       </c>
-      <c r="K44" s="4" t="s">
+      <c r="K44" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2050,9 +2104,9 @@
       <c r="H45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
     </row>
     <row r="46" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -2071,11 +2125,11 @@
         <v>2</v>
       </c>
       <c r="H46" s="1"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="5">
+      <c r="I46" s="4"/>
+      <c r="J46" s="3">
         <v>10</v>
       </c>
-      <c r="K46" s="4" t="s">
+      <c r="K46" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2096,11 +2150,11 @@
         <v>1</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="5">
+      <c r="I47" s="4"/>
+      <c r="J47" s="3">
         <v>50</v>
       </c>
-      <c r="K47" s="4" t="s">
+      <c r="K47" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2121,11 +2175,11 @@
         <v>5</v>
       </c>
       <c r="H48" s="1"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="5">
+      <c r="I48" s="4"/>
+      <c r="J48" s="3">
         <v>50</v>
       </c>
-      <c r="K48" s="4" t="s">
+      <c r="K48" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2146,11 +2200,11 @@
         <v>5</v>
       </c>
       <c r="H49" s="1"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="5">
+      <c r="I49" s="4"/>
+      <c r="J49" s="3">
         <v>50</v>
       </c>
-      <c r="K49" s="4" t="s">
+      <c r="K49" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2171,11 +2225,11 @@
         <v>3</v>
       </c>
       <c r="H50" s="1"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="5">
+      <c r="I50" s="4"/>
+      <c r="J50" s="3">
         <v>50</v>
       </c>
-      <c r="K50" s="4" t="s">
+      <c r="K50" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2200,11 +2254,11 @@
         <v>5</v>
       </c>
       <c r="H51" s="1"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="5">
+      <c r="I51" s="4"/>
+      <c r="J51" s="3">
         <v>20</v>
       </c>
-      <c r="K51" s="4" t="s">
+      <c r="K51" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2229,9 +2283,13 @@
         <v>1</v>
       </c>
       <c r="H52" s="1"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="3">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
@@ -2254,16 +2312,32 @@
         <v>1</v>
       </c>
       <c r="H53" s="1"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="5">
+      <c r="I53" s="4"/>
+      <c r="J53" s="3">
         <v>10</v>
       </c>
-      <c r="K53" s="4" t="s">
-        <v>152</v>
+      <c r="K53" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>